--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-electronics-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-electronics-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Mạch phân áp (Voltage Divider) dùng để hạ áp theo tỷ lệ: $V_{out} = V_{in} \cdot R_2 / (R_1 + R_2)$. Với $R_1 = 2k$ và $R_2 = 3.3k$, khi $V_{in} = 5V$, ta có $V_{out} = 5 \cdot 3.3 / (2 + 3.3) = 3.11V$ (nằm trong khoảng an toàn &lt; 3.3V của ADC). Cần chọn điện trở có sai số nhỏ (1%) để phép đo ADC đạt độ chính xác cao.</v>
       </c>
       <c r="F2" t="str">
+        <v>Nối trực tiếp chân cảm biến 5V vào chân ADC của chip và hy vọng chip có cơ chế tự động bảo vệ sụt áp — kết nối trực tiếp phá hủy chân chip</v>
+      </c>
+      <c r="G2" t="str">
         <v>Thiết kế mạch phân áp (Voltage Divider) sử dụng hai điện trở mắc nối tiếp (ví dụ $R_1 = 2k\Omega$ nối với cảm biến, $R_2 = 3.3k\Omega$ nối xuống đất), lấy điện áp ngõ ra tại điểm giữa hai điện trở cấp vào chân ADC — mạch phân áp bằng hai điện trở</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Mắc nối tiếp một con diode Zener 5V vào chân tín hiệu của cảm biến — diode Zener 5V nối tiếp sai phương pháp</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Lập trình viết code khai báo cấu hình thanh ghi ADC của STM32 tự động nâng giới hạn chịu đựng lên 5V — cấu hình phần mềm không hỗ trợ</v>
       </c>
-      <c r="I2" t="str">
-        <v>Nối trực tiếp chân cảm biến 5V vào chân ADC của chip và hy vọng chip có cơ chế tự động bảo vệ sụt áp — kết nối trực tiếp phá hủy chân chip</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Phím cơ học nảy (Bounce) trong khoảng 5-10ms. Về mặt phần cứng, có thể dùng mạch lọc thông thấp RC (Resistor-Capacitor) để làm mượt sườn xung. Về mặt phần mềm, khi phát hiện nút bấm thay đổi trạng thái, ta chờ khoảng 20ms (delay hoặc dùng timer) và kiểm tra lại trạng thái nút bấm một lần nữa trước khi xác nhận click.</v>
       </c>
       <c r="F3" t="str">
+        <v>Để ngăn chặn bụi bẩn bám vào các tiếp điểm bằng đồng bên trong nút bấm — bảo vệ chống bụi</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Vì nút nhấn bắt buộc phải có thời gian nghỉ 10 giây giữa các lần nhấn theo tiêu chuẩn an toàn lao động — tiêu chuẩn thời gian nghỉ</v>
+      </c>
+      <c r="H3" t="str">
         <v>Vì nút bấm cơ học khi đóng/mở sẽ xảy ra hiện tượng đàn hồi tiếp điểm làm điện áp nhảy vọt liên tục (nảy phím) trong vài mili-giây, khiến MCU nhận diện nhầm thành hàng chục lần nhấn nút — hiện tượng nảy phím cơ học và giải pháp bộ lọc</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Vì khi nhấn nút, dòng điện sẽ tự động đổi chiều liên tục tạo ra sóng điện từ làm sập chip — đảo chiều dòng điện</v>
       </c>
-      <c r="H3" t="str">
-        <v>Để ngăn chặn bụi bẩn bám vào các tiếp điểm bằng đồng bên trong nút bấm — bảo vệ chống bụi</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Vì nút nhấn bắt buộc phải có thời gian nghỉ 10 giây giữa các lần nhấn theo tiêu chuẩn an toàn lao động — tiêu chuẩn thời gian nghỉ</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>MOSFET thông thường (như IRFZ44N) cần điện áp $V_{GS}$ khoảng 10V để mở dẫn hoàn toàn. Nếu điều khiển bằng chân MCU 5V hoặc 3.3V, MOSFET chỉ mở hé (vùng tuyến tính), điện trở kênh $R_{DS(on)}$ rất lớn. Khi có dòng lớn đi qua, MOSFET sẽ tiêu tán nhiệt cực mạnh ($P = I^2 \cdot R$) và tự cháy sau vài giây. Logic-Level MOSFET giải quyết bằng cách bão hòa hoàn toàn ở $V_{GS} &lt; 4V$.</v>
       </c>
       <c r="F4" t="str">
-        <v>Vì Logic-Level MOSFET có điện áp ngưỡng mở kênh ($V_{GS(th)}$) cực thấp, cho phép MOSFET mở dẫn hoàn toàn (đạt trạng thái bão hòa có $R_{DS(on)}$ nhỏ nhất) ở mức áp điều khiển 3.3V/5V, tránh việc MOSFET bị nóng và cháy — điện áp ngưỡng mở thấp bão hòa hoàn toàn ở mức logic MCU</v>
+        <v>Để đảm bảo dòng điện chạy qua động cơ tự động đảo chiều khi vi điều khiển bị sập nguồn — tự đảo dòng</v>
       </c>
       <c r="G4" t="str">
         <v>Vì Logic-Level MOSFET tự động điều chỉnh tốc độ quay của động cơ bước theo chu kỳ SysTick — điều tốc động cơ</v>
@@ -533,10 +533,10 @@
         <v>Vì MOSFET thông thường (như IRFZ44N) chỉ hoạt động được khi chân điều khiển nhận tín hiệu dòng điện xoay chiều — yêu cầu dòng xoay chiều</v>
       </c>
       <c r="I4" t="str">
-        <v>Để đảm bảo dòng điện chạy qua động cơ tự động đảo chiều khi vi điều khiển bị sập nguồn — tự đảo dòng</v>
+        <v>Vì Logic-Level MOSFET có điện áp ngưỡng mở kênh ($V_{GS(th)}$) cực thấp, cho phép MOSFET mở dẫn hoàn toàn (đạt trạng thái bão hòa có $R_{DS(on)}$ nhỏ nhất) ở mức áp điều khiển 3.3V/5V, tránh việc MOSFET bị nóng và cháy — điện áp ngưỡng mở thấp bão hòa hoàn toàn ở mức logic MCU</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Dòng điện luôn chạy theo một vòng kín. Tín hiệu tần số cao (AC) có xu hướng chạy trên đường hồi có trở kháng nhỏ nhất (chạy trực tiếp bên dưới đường chạy dây tín hiệu ở lớp đối diện). Ground Plane cung cấp đường hồi tự nhiên này ngay sát dây tín hiệu, giảm diện tích vòng lặp dòng điện xuống tối thiểu, ngăn ngừa bo mạch trở thành một ăng-ten phát hoặc thu nhiễu điện từ (EMI).</v>
       </c>
       <c r="F5" t="str">
+        <v>Để tiết kiệm lượng axit cần thiết để ăn mòn các lớp đồng thừa khi gia công mạch — tiết kiệm axit ăn mòn</v>
+      </c>
+      <c r="G5" t="str">
         <v>Để cung cấp đường hồi dòng (Return Path) có trở kháng cực thấp cho các tín hiệu tần số cao, giảm thiểu tối đa diện tích vòng lặp dòng điện (Current Loop Area) giúp triệt tiêu bức xạ điện từ và chống nhiễu chéo chằng chịt — đường hồi dòng trở kháng thấp giảm diện tích vòng lặp nhiễu</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Để đảm bảo bo mạch PCB không bị cong vênh khi đi qua lò hàn nhiệt độ cao 250 độ C — chống cong vênh mạch</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Để tiết kiệm lượng axit cần thiết để ăn mòn các lớp đồng thừa khi gia công mạch — tiết kiệm axit ăn mòn</v>
       </c>
       <c r="I5" t="str">
         <v>Để ngăn chặn các cuộc tấn công đánh cắp firmware từ chip thông qua các cổng nạp phần cứng — chống hack firmware</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Nếu chọn trở Shunt lớn (ví dụ 10 Ohm, dòng 1A), sụt áp trên Shunt là 10V (tải không chạy được) và trở sinh nhiệt 10W (cháy điện trở). Chọn trở Shunt cực nhỏ ($10m\Omega$) giúp sụt áp chỉ 10mV, ít tổn hao. Vì 10mV quá nhỏ so với thang đo ADC (thường 0-3.3V), ta bắt buộc phải dùng mạch khuếch đại thuật toán (Op-Amp) hoặc IC chuyên dụng để nhân điện áp này lên khoảng 50-100 lần.</v>
       </c>
       <c r="F6" t="str">
+        <v>Chọn điện trở Shunt có giá trị lớn (ví dụ $10k\Omega$) để điện áp rơi trên nó lớn bằng đúng 5V cho ADC dễ đọc trực tiếp — chọn trở Shunt lớn sai phương pháp làm sập nguồn tải</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Lập trình viết code tự động nhân giá trị đọc được từ ADC lên 1000 lần để bù đắp sụt áp — nhân giá trị phần mềm</v>
+      </c>
+      <c r="H6" t="str">
         <v>Chọn điện trở Shunt có giá trị cực nhỏ (ví dụ $0.01 \Omega$ hoặc $0.1 \Omega$) để giảm hao phí điện áp và nhiệt trên điện trở, kết hợp sử dụng IC khuếch đại vi sai đo dòng chuyên dụng (Current Sense Amplifier) để phóng to hiệu điện áp cực nhỏ trên Shunt trước khi cấp vào ADC — điện trở Shunt nhỏ và IC khuếch đại vi sai</v>
       </c>
-      <c r="G6" t="str">
-        <v>Chọn điện trở Shunt có giá trị lớn (ví dụ $10k\Omega$) để điện áp rơi trên nó lớn bằng đúng 5V cho ADC dễ đọc trực tiếp — chọn trở Shunt lớn sai phương pháp làm sập nguồn tải</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Mắc song song một con tụ điện dung lượng lớn 10,000uF vào hai đầu điện trở Shunt — mắc tụ lọc dòng cực đoan</v>
       </c>
-      <c r="I6" t="str">
-        <v>Lập trình viết code tự động nhân giá trị đọc được từ ADC lên 1000 lần để bù đắp sụt áp — nhân giá trị phần mềm</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Vì chế độ x10 tăng trở kháng đầu vào của probe lên cực lớn ($10M\Omega$) và giảm điện dung ký sinh xuống tối thiểu (vài pF), giúp giảm hiệu ứng tải (Loading Effect) không làm biến dạng tín hiệu mạch cần đo — thang đo x10 giảm loading effect bảo toàn toàn vẹn tín hiệu</v>
       </c>
       <c r="G7" t="str">
+        <v>Vì chế độ x10 bắt buộc máy dao động ký phải sử dụng nguồn điện xoay chiều 220V để hoạt động — nguồn điện hoạt động máy</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Vì chế độ x10 tự động khóa toàn bộ các ngắt của vi điều khiển trên bo mạch cần đo — tắt ngắt chéo chân chip</v>
+      </c>
+      <c r="I7" t="str">
         <v>Vì chế độ x10 tự động phóng to hình ảnh dạng sóng hiển thị trên màn hình dao động ký lên gấp 10 lần cho dễ nhìn — phóng to màn hình hiển thị</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Vì chế độ x10 bắt buộc máy dao động ký phải sử dụng nguồn điện xoay chiều 220V để hoạt động — nguồn điện hoạt động máy</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Vì chế độ x10 tự động khóa toàn bộ các ngắt của vi điều khiển trên bo mạch cần đo — tắt ngắt chéo chân chip</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>TVS Diode hoạt động như một diode Zener phản ứng cực nhanh (cỡ picoseconds). Khi điện áp đột ngột tăng vượt quá điện áp đánh thủng của TVS, diode lập tức mở dẫn dòng, kẹp chặt điện áp (Clamping) ở mức an toàn và chuyển hướng toàn bộ dòng điện sốc xuống đất GND, bảo vệ mạch nguồn phía sau.</v>
       </c>
       <c r="F8" t="str">
+        <v>Lập trình viết code cho vi điều khiển tự động xả bớt điện áp dư thừa ra các chân GPIO rảnh — xả điện áp phần mềm qua GPIO</v>
+      </c>
+      <c r="G8" t="str">
         <v>Sử dụng diode dập điện áp chuyển tiếp (TVS Diode - Transient Voltage Suppressor) hoặc Varistor (MOV) mắc song song với đường nguồn đầu vào ngay sau cầu chì — TVS diode dập điện áp quá áp bảo vệ nguồn</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Sử dụng một cuộn cảm có lõi không khí mắc song song với đường nguồn cấp — cuộn cảm song song nguồn</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Cài đặt một chiếc rơ-le thời gian tự động ngắt nguồn điện sau mỗi 10 phút sử dụng — rơ-le thời gian ngắt định kỳ</v>
       </c>
-      <c r="I8" t="str">
-        <v>Lập trình viết code cho vi điều khiển tự động xả bớt điện áp dư thừa ra các chân GPIO rảnh — xả điện áp phần mềm qua GPIO</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Nhiễu chuyển mạch kỹ thuật số (digital switching noise) tạo ra các dòng gai (noise currents) chạy trên mặt phẳng đất. Nếu dùng chung GND hỗn loạn, dòng nhiễu này sẽ chạy qua vùng đất analog nhạy cảm, tạo ra sụt áp nhiễu làm sai số đọc ADC. Phân tách đất và chỉ nối tại 1 điểm (Star Ground) đảm bảo dòng nhiễu digital không thể chạy xuyên qua khu vực analog.</v>
       </c>
       <c r="F9" t="str">
-        <v>Phân tách mặt phẳng đất thành đất Analog (AGND) và đất Digital (DGND) độc lập, chỉ nối chúng lại với nhau tại một điểm duy nhất (Single-point/Star ground) gần chân nguồn hoặc dùng cuộn cảm hạt ferrite (Ferrite bead) — phân tách AGND/DGND liên kết star ground</v>
+        <v>Yêu cầu cơ sở sản xuất mạch in PCB mạ vàng toàn bộ mặt sau của bảng mạch in — mạ vàng mặt sau PCB</v>
       </c>
       <c r="G9" t="str">
         <v>Nối chung toàn bộ đất Analog và đất Digital chạy hỗn loạn chằng chịt trên cùng một lớp tín hiệu — chạy dây đất hỗn loạn gây nhiễu nặng</v>
       </c>
       <c r="H9" t="str">
+        <v>Phân tách mặt phẳng đất thành đất Analog (AGND) và đất Digital (DGND) độc lập, chỉ nối chúng lại với nhau tại một điểm duy nhất (Single-point/Star ground) gần chân nguồn hoặc dùng cuộn cảm hạt ferrite (Ferrite bead) — phân tách AGND/DGND liên kết star ground</v>
+      </c>
+      <c r="I9" t="str">
         <v>Bỏ qua việc vẽ đường chạy dây đất cho khối Analog để nó tự hoạt động lơ lửng — cách ly đất khối analog</v>
       </c>
-      <c r="I9" t="str">
-        <v>Yêu cầu cơ sở sản xuất mạch in PCB mạ vàng toàn bộ mặt sau của bảng mạch in — mạ vàng mặt sau PCB</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Trong Buck converter, cuộn cảm tích lũy năng lượng dưới dạng từ trường khi van đóng và phóng điện khi van mở. Tụ điện san phẳng điện áp gợn sóng. Trị số gợn sóng phụ thuộc lớn vào điện trở ký sinh ESR (Equivalent Series Resistance) của tụ. Chọn tụ có Low-ESR (như tụ Polymer hoặc tụ gốm MLCC) là bắt buộc ở tần số cao.</v>
       </c>
       <c r="F10" t="str">
+        <v>Sử dụng một điện trở công suất lớn 100 Ohm mắc nối tiếp với diode Zener 5V — mạch ổn áp zener công suất thấp lãng phí năng lượng</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Sử dụng một IC cách ly quang (Optocoupler) mắc nối tiếp giữa nguồn 12V và 5V — optocoupler nối tiếp nguồn</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Lập trình viết code cho vi điều khiển tự động thay đổi tần số PWM của mạch Buck liên tục sau mỗi 1 microsecond — thay đổi tần số PWM liên tục</v>
+      </c>
+      <c r="I10" t="str">
         <v>Cuộn cảm (Inductor) và Tụ điện ngõ ra (Output Capacitor) tạo thành bộ lọc thông thấp LC; cần tính toán trị số cuộn cảm ($L$) và điện trở ký sinh ESR của tụ điện đủ nhỏ để giảm gợn sóng dòng điện — bộ lọc LC và ESR tụ điện ngõ ra</v>
       </c>
-      <c r="G10" t="str">
-        <v>Sử dụng một điện trở công suất lớn 100 Ohm mắc nối tiếp với diode Zener 5V — mạch ổn áp zener công suất thấp lãng phí năng lượng</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Sử dụng một IC cách ly quang (Optocoupler) mắc nối tiếp giữa nguồn 12V và 5V — optocoupler nối tiếp nguồn</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Lập trình viết code cho vi điều khiển tự động thay đổi tần số PWM của mạch Buck liên tục sau mỗi 1 microsecond — thay đổi tần số PWM liên tục</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Tiếp điểm rơ-le khi đóng/cắt tải AC lớn sẽ tạo ra tia lửa điện (hồ quang - Arcing). Hồ quang phát ra nhiễu sóng điện từ cực mạnh (EMI) lan truyền qua không khí hoặc đường nguồn làm treo CPU. Snubber RC mắc song song tiếp điểm hấp thụ năng lượng hồ quang tại thời điểm ngắt tiếp điểm, dập tắt tia lửa điện hoàn toàn.</v>
       </c>
       <c r="F11" t="str">
-        <v>Mắc mạch dập nhiễu RC (Snubber Circuit - gồm điện trở và tụ điện nối tiếp) hoặc Varistor (MOV) song song với tiếp điểm của Rơ-le — mạch Snubber RC dập hồ quang điện tiếp điểm</v>
+        <v>Mắc một chiếc diode Flyback ngược song song với tiếp điểm rơ-le phía dòng AC — diode ngược dòng AC không hoạt động gây ngắn mạch</v>
       </c>
       <c r="G11" t="str">
-        <v>Mắc một chiếc diode Flyback ngược song song với tiếp điểm rơ-le phía dòng AC — diode ngược dòng AC không hoạt động gây ngắn mạch</v>
+        <v>Lập trình viết code tăng gấp đôi thời gian feed watchdog timer của vi điều khiển — kéo dài thời gian feed WDT tránh triệu chứng</v>
       </c>
       <c r="H11" t="str">
         <v>Thay thế toàn bộ vỏ nhựa của rơ-le bằng vỏ sắt dày 5mm để cản bức xạ — bọc vỏ sắt rơ-le</v>
       </c>
       <c r="I11" t="str">
-        <v>Lập trình viết code tăng gấp đôi thời gian feed watchdog timer của vi điều khiển — kéo dài thời gian feed WDT tránh triệu chứng</v>
+        <v>Mắc mạch dập nhiễu RC (Snubber Circuit - gồm điện trở và tụ điện nối tiếp) hoặc Varistor (MOV) song song với tiếp điểm của Rơ-le — mạch Snubber RC dập hồ quang điện tiếp điểm</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
